--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N71_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N71_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.51905189217689</v>
+        <v>5.121845932478744</v>
       </c>
       <c r="D2" t="n">
-        <v>29.1563321467373</v>
+        <v>4.737903973844811</v>
       </c>
       <c r="E2" t="n">
-        <v>11.70486418463042</v>
+        <v>1.902040430002442</v>
       </c>
       <c r="F2" t="n">
-        <v>10.29024165847576</v>
+        <v>1.67216426950231</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>7.425730493204457</v>
+        <v>1.206681205145724</v>
       </c>
       <c r="D3" t="n">
-        <v>5.364319059748288</v>
+        <v>0.8717018472090968</v>
       </c>
       <c r="E3" t="n">
-        <v>11.70486418463042</v>
+        <v>1.902040430002442</v>
       </c>
       <c r="F3" t="n">
-        <v>10.29024165847576</v>
+        <v>1.67216426950231</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.47866972547569</v>
+        <v>2.352783830389799</v>
       </c>
       <c r="D4" t="n">
-        <v>13.11763830172467</v>
+        <v>2.131616224030259</v>
       </c>
       <c r="E4" t="n">
-        <v>11.70486418463042</v>
+        <v>1.902040430002442</v>
       </c>
       <c r="F4" t="n">
-        <v>10.29024165847576</v>
+        <v>1.67216426950231</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.25522747384303</v>
+        <v>2.803974464499493</v>
       </c>
       <c r="D5" t="n">
-        <v>19.62898428144563</v>
+        <v>3.189709945734915</v>
       </c>
       <c r="E5" t="n">
-        <v>11.70486418463042</v>
+        <v>1.902040430002442</v>
       </c>
       <c r="F5" t="n">
-        <v>10.29024165847576</v>
+        <v>1.67216426950231</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>46.10220993873123</v>
+        <v>7.491609115043825</v>
       </c>
       <c r="D6" t="n">
-        <v>42.39279668979486</v>
+        <v>6.888829462091666</v>
       </c>
       <c r="E6" t="n">
-        <v>11.70486418463042</v>
+        <v>1.902040430002442</v>
       </c>
       <c r="F6" t="n">
-        <v>10.29024165847576</v>
+        <v>1.67216426950231</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>45.2307555731177</v>
+        <v>7.349997780631627</v>
       </c>
       <c r="D7" t="n">
-        <v>38.1390907120104</v>
+        <v>6.19760224070169</v>
       </c>
       <c r="E7" t="n">
-        <v>11.70486418463042</v>
+        <v>1.902040430002442</v>
       </c>
       <c r="F7" t="n">
-        <v>10.29024165847576</v>
+        <v>1.67216426950231</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.14340993308262</v>
+        <v>4.573304114125927</v>
       </c>
       <c r="D8" t="n">
-        <v>17.70249957563579</v>
+        <v>2.876656181040816</v>
       </c>
       <c r="E8" t="n">
-        <v>11.70486418463042</v>
+        <v>1.902040430002442</v>
       </c>
       <c r="F8" t="n">
-        <v>10.29024165847576</v>
+        <v>1.67216426950231</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>36.88297231901448</v>
+        <v>5.993483001839853</v>
       </c>
       <c r="D9" t="n">
-        <v>34.11857478153896</v>
+        <v>5.544268402000081</v>
       </c>
       <c r="E9" t="n">
-        <v>11.70486418463042</v>
+        <v>1.902040430002442</v>
       </c>
       <c r="F9" t="n">
-        <v>10.29024165847576</v>
+        <v>1.67216426950231</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>38.14860411329455</v>
+        <v>6.199148168410364</v>
       </c>
       <c r="D10" t="n">
-        <v>15.40944976225007</v>
+        <v>2.504035586365636</v>
       </c>
       <c r="E10" t="n">
-        <v>11.70486418463042</v>
+        <v>1.902040430002442</v>
       </c>
       <c r="F10" t="n">
-        <v>10.29024165847576</v>
+        <v>1.67216426950231</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>44.51003704555172</v>
+        <v>7.232881019902154</v>
       </c>
       <c r="D11" t="n">
-        <v>38.04731203954649</v>
+        <v>6.182688206426305</v>
       </c>
       <c r="E11" t="n">
-        <v>11.70486418463042</v>
+        <v>1.902040430002442</v>
       </c>
       <c r="F11" t="n">
-        <v>10.29024165847576</v>
+        <v>1.67216426950231</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>23.63340817553916</v>
+        <v>3.840428828525114</v>
       </c>
       <c r="D12" t="n">
-        <v>24.01217011727512</v>
+        <v>3.901977644057206</v>
       </c>
       <c r="E12" t="n">
-        <v>11.70486418463042</v>
+        <v>1.902040430002442</v>
       </c>
       <c r="F12" t="n">
-        <v>10.29024165847576</v>
+        <v>1.67216426950231</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>29.40084250634202</v>
+        <v>4.777636907280579</v>
       </c>
       <c r="D13" t="n">
-        <v>22.827661965526</v>
+        <v>3.709495069397975</v>
       </c>
       <c r="E13" t="n">
-        <v>11.70486418463042</v>
+        <v>1.902040430002442</v>
       </c>
       <c r="F13" t="n">
-        <v>10.29024165847576</v>
+        <v>1.67216426950231</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>12.32237690280707</v>
+        <v>2.00238624670615</v>
       </c>
       <c r="D14" t="n">
-        <v>16.95854301082856</v>
+        <v>2.755763239259642</v>
       </c>
       <c r="E14" t="n">
-        <v>11.70486418463042</v>
+        <v>1.902040430002442</v>
       </c>
       <c r="F14" t="n">
-        <v>10.29024165847576</v>
+        <v>1.67216426950231</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>9.628904477247858</v>
+        <v>1.564696977552777</v>
       </c>
       <c r="D15" t="n">
-        <v>3.559325040424942</v>
+        <v>0.5783903190690531</v>
       </c>
       <c r="E15" t="n">
-        <v>11.70486418463042</v>
+        <v>1.902040430002442</v>
       </c>
       <c r="F15" t="n">
-        <v>10.29024165847576</v>
+        <v>1.67216426950231</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>30.70030718390359</v>
+        <v>4.988799917384334</v>
       </c>
       <c r="D16" t="n">
-        <v>5.998288710592489</v>
+        <v>0.9747219154712795</v>
       </c>
       <c r="E16" t="n">
-        <v>11.70486418463042</v>
+        <v>1.902040430002442</v>
       </c>
       <c r="F16" t="n">
-        <v>10.29024165847576</v>
+        <v>1.67216426950231</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>25.95691269805621</v>
+        <v>4.217998313434134</v>
       </c>
       <c r="D17" t="n">
-        <v>6.842093345636996</v>
+        <v>1.111840168666012</v>
       </c>
       <c r="E17" t="n">
-        <v>11.70486418463042</v>
+        <v>1.902040430002442</v>
       </c>
       <c r="F17" t="n">
-        <v>10.29024165847576</v>
+        <v>1.67216426950231</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>23.89764745316373</v>
+        <v>3.883367711139106</v>
       </c>
       <c r="D18" t="n">
-        <v>9.590472004027276</v>
+        <v>1.558451700654433</v>
       </c>
       <c r="E18" t="n">
-        <v>11.70486418463042</v>
+        <v>1.902040430002442</v>
       </c>
       <c r="F18" t="n">
-        <v>10.29024165847576</v>
+        <v>1.67216426950231</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>21.05472947498316</v>
+        <v>3.421393539684763</v>
       </c>
       <c r="D19" t="n">
-        <v>12.73588854232926</v>
+        <v>2.069581888128504</v>
       </c>
       <c r="E19" t="n">
-        <v>11.70486418463042</v>
+        <v>1.902040430002442</v>
       </c>
       <c r="F19" t="n">
-        <v>10.29024165847576</v>
+        <v>1.67216426950231</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>32.20417922990469</v>
+        <v>5.233179124859512</v>
       </c>
       <c r="D20" t="n">
-        <v>14.03547342882105</v>
+        <v>2.280764432183422</v>
       </c>
       <c r="E20" t="n">
-        <v>11.70486418463042</v>
+        <v>1.902040430002442</v>
       </c>
       <c r="F20" t="n">
-        <v>10.29024165847576</v>
+        <v>1.67216426950231</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>21.57842145866473</v>
+        <v>3.506493487033019</v>
       </c>
       <c r="D21" t="n">
-        <v>17.51427799557827</v>
+        <v>2.846070174281469</v>
       </c>
       <c r="E21" t="n">
-        <v>11.70486418463042</v>
+        <v>1.902040430002442</v>
       </c>
       <c r="F21" t="n">
-        <v>10.29024165847576</v>
+        <v>1.67216426950231</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>29.58984843884135</v>
+        <v>4.808350371311719</v>
       </c>
       <c r="D22" t="n">
-        <v>25.70992026436488</v>
+        <v>4.177862042959293</v>
       </c>
       <c r="E22" t="n">
-        <v>11.70486418463042</v>
+        <v>1.902040430002442</v>
       </c>
       <c r="F22" t="n">
-        <v>10.29024165847576</v>
+        <v>1.67216426950231</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>40.39166602701035</v>
+        <v>6.563645729389182</v>
       </c>
       <c r="D23" t="n">
-        <v>16.29120599864878</v>
+        <v>2.647320974780427</v>
       </c>
       <c r="E23" t="n">
-        <v>11.70486418463042</v>
+        <v>1.902040430002442</v>
       </c>
       <c r="F23" t="n">
-        <v>10.29024165847576</v>
+        <v>1.67216426950231</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>38.74774167975916</v>
+        <v>6.296508022960864</v>
       </c>
       <c r="D24" t="n">
-        <v>17.98709649987645</v>
+        <v>2.922903181229923</v>
       </c>
       <c r="E24" t="n">
-        <v>11.70486418463042</v>
+        <v>1.902040430002442</v>
       </c>
       <c r="F24" t="n">
-        <v>10.29024165847576</v>
+        <v>1.67216426950231</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>41.20014872319181</v>
+        <v>6.695024167518669</v>
       </c>
       <c r="D25" t="n">
-        <v>12.47243654447784</v>
+        <v>2.026770938477648</v>
       </c>
       <c r="E25" t="n">
-        <v>11.70486418463042</v>
+        <v>1.902040430002442</v>
       </c>
       <c r="F25" t="n">
-        <v>10.29024165847576</v>
+        <v>1.67216426950231</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>43.98814837066387</v>
+        <v>7.148074110232879</v>
       </c>
       <c r="D26" t="n">
-        <v>19.5</v>
+        <v>3.16875</v>
       </c>
       <c r="E26" t="n">
-        <v>11.70486418463042</v>
+        <v>1.902040430002442</v>
       </c>
       <c r="F26" t="n">
-        <v>10.29024165847576</v>
+        <v>1.67216426950231</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>10.17090596532102</v>
+        <v>1.652772219364665</v>
       </c>
       <c r="D27" t="n">
-        <v>11.25557077069042</v>
+        <v>1.829030250237193</v>
       </c>
       <c r="E27" t="n">
-        <v>11.70486418463042</v>
+        <v>1.902040430002442</v>
       </c>
       <c r="F27" t="n">
-        <v>10.29024165847576</v>
+        <v>1.67216426950231</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
